--- a/backend/app/templates/IMPORT_K3_Смартфоны.xlsx
+++ b/backend/app/templates/IMPORT_K3_Смартфоны.xlsx
@@ -495,7 +495,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -508,20 +508,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
-      <top/>
-      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
@@ -555,47 +541,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -911,543 +897,543 @@
   <dimension ref="A1:AD10"/>
   <sheetFormatPr defaultColWidth="8.43359375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="31" style="0" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="31" style="1" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="H3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="P3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="R3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD3" s="2" t="s">
+      <c r="R3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD3" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="T4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="U4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="W4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="X4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Y4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="Z4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AA4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AB4" s="3" t="s">
+      <c r="AB4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AC4" s="3" t="s">
+      <c r="AC4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AD4" s="4" t="s">
+      <c r="AD4" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
+      <c r="A5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
       <c r="K6" s="9"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
       <c r="H7" s="8"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
       <c r="K7" s="9"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="6"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
       <c r="K8" s="9"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="6"/>
+      <c r="O8" s="7"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
       <c r="T8" s="9"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="6"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
       <c r="H9" s="8"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
       <c r="K9" s="9"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="6"/>
+      <c r="O9" s="7"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
       <c r="T9" s="9"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="6"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
       <c r="H10" s="8"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="9"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="6"/>
+      <c r="O10" s="7"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1476,9 +1462,9 @@
   <dimension ref="A1:B97"/>
   <sheetFormatPr defaultColWidth="8.43359375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="3" style="0" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="3" style="1" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1488,7 +1474,7 @@
       <c r="B1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5"/>
+      <c r="A2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
@@ -1497,15 +1483,15 @@
       <c r="B3" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5"/>
+      <c r="A5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
+      <c r="A6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
@@ -1524,608 +1510,608 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="5" t="s">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="5" t="s">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="5" t="s">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="5" t="s">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="5" t="s">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="5" t="s">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="5" t="s">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="5" t="s">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="5" t="s">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="5" t="s">
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="5" t="s">
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="A42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="5" t="s">
+      <c r="A45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="5" t="s">
+      <c r="A46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" s="5" t="s">
+      <c r="A47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="5" t="s">
+      <c r="A48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" s="5" t="s">
+      <c r="A49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="5" t="s">
+      <c r="A50" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="5" t="s">
+      <c r="A51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="5" t="s">
+      <c r="A52" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" s="5" t="s">
+      <c r="A53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54" s="5" t="s">
+      <c r="A54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" s="5" t="s">
+      <c r="A55" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="A56" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" s="5" t="s">
+      <c r="A57" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" s="5" t="s">
+      <c r="A58" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59" s="5" t="s">
+      <c r="A59" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="A60" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B61" s="5" t="s">
+      <c r="A61" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B62" s="5" t="s">
+      <c r="A62" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63" s="5" t="s">
+      <c r="A63" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B64" s="5" t="s">
+      <c r="A64" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65" s="5" t="s">
+      <c r="A65" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B66" s="5" t="s">
+      <c r="A66" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B67" s="5" t="s">
+      <c r="A67" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="6" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5" t="s">
+      <c r="A73" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="6" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="6" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="6" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="6" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="6" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="5" t="s">
+      <c r="A83" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="6" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5"/>
-      <c r="B85" s="5"/>
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="6" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5"/>
-      <c r="B90" s="5"/>
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="5" t="s">
+      <c r="A91" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="6" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="6" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="5"/>
-      <c r="B93" s="5"/>
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="5"/>
-      <c r="B94" s="5"/>
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="5"/>
-      <c r="B95" s="5"/>
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="5"/>
-      <c r="B96" s="5"/>
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="5"/>
-      <c r="B97" s="5"/>
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/backend/app/templates/IMPORT_K3_Смартфоны.xlsx
+++ b/backend/app/templates/IMPORT_K3_Смартфоны.xlsx
@@ -420,7 +420,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -456,12 +456,6 @@
       <family val="3"/>
       <charset val="204"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -495,7 +489,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -508,6 +502,13 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -536,52 +537,72 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -894,398 +915,398 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr defaultColWidth="8.43359375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="31" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="61.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="31" style="0" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="X2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Y2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Z2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AA2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AB2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AC2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="O3" s="3" t="s">
+      <c r="H3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q3" s="3" t="s">
+      <c r="P3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="R3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD3" s="3" t="s">
+      <c r="R3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD3" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="T4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="U4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="V4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="W4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="X4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Y4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="Z4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AA4" s="4" t="s">
+      <c r="AA4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AB4" s="4" t="s">
+      <c r="AB4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AC4" s="4" t="s">
+      <c r="AC4" s="3" t="s">
         <v>61</v>
       </c>
       <c r="AD4" s="5" t="s">
@@ -1294,24 +1315,24 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
+      <c r="K5" s="9"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
+      <c r="N5" s="9"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
     </row>
@@ -1319,23 +1340,22 @@
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="9"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="9"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
+      <c r="N6" s="9"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
     </row>
@@ -1343,23 +1363,22 @@
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="9"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="9"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+      <c r="N7" s="9"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
     </row>
@@ -1367,11 +1386,10 @@
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="6"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="9"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="9"/>
@@ -1379,8 +1397,8 @@
       <c r="M8" s="7"/>
       <c r="N8" s="9"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
       <c r="T8" s="9"/>
@@ -1391,11 +1409,10 @@
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="6"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="9"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="9"/>
@@ -1403,8 +1420,8 @@
       <c r="M9" s="7"/>
       <c r="N9" s="9"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
       <c r="T9" s="9"/>
@@ -1415,11 +1432,10 @@
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="6"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="9"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="9"/>
@@ -1427,13 +1443,40 @@
       <c r="M10" s="7"/>
       <c r="N10" s="9"/>
       <c r="O10" s="7"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1462,656 +1505,656 @@
   <dimension ref="A1:B97"/>
   <sheetFormatPr defaultColWidth="8.43359375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="3" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="3" style="0" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="15"/>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6"/>
+      <c r="A2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="11"/>
+      <c r="B3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="13" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6"/>
+      <c r="A5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6"/>
+      <c r="A6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="16" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="16" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="13" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="13" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="13" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="13" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="13" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="13" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="13" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="13" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="6" t="s">
+      <c r="A24" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="A25" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="6" t="s">
+      <c r="A26" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="6" t="s">
+      <c r="A27" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="13" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="6" t="s">
+      <c r="A28" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="A29" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="6" t="s">
+      <c r="A30" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="A31" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="6" t="s">
+      <c r="A32" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="6" t="s">
+      <c r="A33" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="6" t="s">
+      <c r="A34" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="6" t="s">
+      <c r="A35" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="6" t="s">
+      <c r="A36" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="13" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="6" t="s">
+      <c r="A37" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="13" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="6" t="s">
+      <c r="A38" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="13" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" s="6" t="s">
+      <c r="A39" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="13" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" s="6" t="s">
+      <c r="A40" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="6" t="s">
+      <c r="A41" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="6" t="s">
+      <c r="A42" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" s="6" t="s">
+      <c r="A43" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="13" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" s="6" t="s">
+      <c r="A44" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="6" t="s">
+      <c r="A45" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="13" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="6" t="s">
+      <c r="A46" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" s="6" t="s">
+      <c r="A47" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="13" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="6" t="s">
+      <c r="A48" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="13" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" s="6" t="s">
+      <c r="A49" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="13" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="6" t="s">
+      <c r="A50" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="13" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="6" t="s">
+      <c r="A51" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="6" t="s">
+      <c r="A52" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="13" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" s="6" t="s">
+      <c r="A53" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="13" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54" s="6" t="s">
+      <c r="A54" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" s="6" t="s">
+      <c r="A55" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="13" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" s="6" t="s">
+      <c r="A56" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="13" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" s="6" t="s">
+      <c r="A57" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" s="6" t="s">
+      <c r="A58" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="A59" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="A60" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="13" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B61" s="6" t="s">
+      <c r="A61" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="13" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B62" s="6" t="s">
+      <c r="A62" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="13" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63" s="6" t="s">
+      <c r="A63" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="13" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B64" s="6" t="s">
+      <c r="A64" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" s="13" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65" s="6" t="s">
+      <c r="A65" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="13" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B66" s="6" t="s">
+      <c r="A66" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" s="13" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B67" s="6" t="s">
+      <c r="A67" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" s="13" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
+      <c r="A68" s="13"/>
+      <c r="B68" s="13"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="13" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
+      <c r="A71" s="13"/>
+      <c r="B71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
+      <c r="A72" s="13"/>
+      <c r="B72" s="13"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="13" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
+      <c r="A74" s="13"/>
+      <c r="B74" s="13"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
+      <c r="A75" s="13"/>
+      <c r="B75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
+      <c r="A76" s="13"/>
+      <c r="B76" s="13"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="13" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="13" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
+      <c r="A79" s="13"/>
+      <c r="B79" s="13"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
+      <c r="A80" s="13"/>
+      <c r="B80" s="13"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="13" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="13" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="13" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
+      <c r="A84" s="13"/>
+      <c r="B84" s="13"/>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
+      <c r="A85" s="13"/>
+      <c r="B85" s="13"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
+      <c r="A86" s="13"/>
+      <c r="B86" s="13"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
+      <c r="A87" s="13"/>
+      <c r="B87" s="13"/>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="13" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
+      <c r="A89" s="13"/>
+      <c r="B89" s="13"/>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
+      <c r="A90" s="13"/>
+      <c r="B90" s="13"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="13" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
+      <c r="A93" s="13"/>
+      <c r="B93" s="13"/>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
+      <c r="A94" s="13"/>
+      <c r="B94" s="13"/>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
+      <c r="A95" s="13"/>
+      <c r="B95" s="13"/>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
+      <c r="A96" s="13"/>
+      <c r="B96" s="13"/>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
+      <c r="A97" s="13"/>
+      <c r="B97" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
